--- a/data/trans_bre/IP1001-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 5,05</t>
+          <t>-0,63; 4,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 0,0</t>
+          <t>-6,01; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 2,45</t>
+          <t>-5,16; 2,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 4,43</t>
+          <t>-8,82; 4,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 247,09</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 6,16</t>
+          <t>-2,58; 6,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,99</t>
+          <t>-4,15; 1,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,06; -0,97</t>
+          <t>-5,95; -1,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 2,69</t>
+          <t>-7,84; 3,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,62; inf</t>
+          <t>-66,9; 758,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 403,1</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 2,21</t>
+          <t>-7,76; 2,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,63</t>
+          <t>-2,63; 1,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 2,5</t>
+          <t>-7,45; 2,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 5,74</t>
+          <t>-1,57; 7,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 91,01</t>
+          <t>-90,56; 137,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 2,32</t>
+          <t>-2,35; 2,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 3,06</t>
+          <t>-2,74; 3,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,96</t>
+          <t>-2,61; 1,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 1,14</t>
+          <t>-4,75; 1,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,39; 189,58</t>
+          <t>-71,31; 208,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,01; 169,86</t>
+          <t>-59,41; 151,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,95; 225,07</t>
+          <t>-80,14; 259,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,99; 61,24</t>
+          <t>-82,25; 54,54</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 6,44</t>
+          <t>-1,82; 6,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 2,98</t>
+          <t>-4,17; 2,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 4,37</t>
+          <t>-2,87; 4,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,07</t>
+          <t>-4,35; 1,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-48,8; 690,69</t>
+          <t>-55,96; 534,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-82,38; 268,17</t>
+          <t>-86,58; 226,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-74,59; 320,18</t>
+          <t>-68,37; 345,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 219,73</t>
+          <t>-100,0; 255,36</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 5,7</t>
+          <t>-1,81; 5,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 0,0</t>
+          <t>-6,58; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 7,85</t>
+          <t>-1,12; 7,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,04; -1,1</t>
+          <t>-12,73; -0,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,79</t>
+          <t>-1,06; 1,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,76</t>
+          <t>-1,98; 0,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,74</t>
+          <t>-1,89; 0,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,15</t>
+          <t>-3,34; 0,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-35,25; 88,78</t>
+          <t>-31,77; 91,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-56,24; 47,76</t>
+          <t>-62,17; 43,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-55,37; 38,37</t>
+          <t>-55,89; 38,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-68,63; 13,08</t>
+          <t>-69,15; 7,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1001-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,82</t>
+          <t>-0,63; 4,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 0,0</t>
+          <t>-5,92; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 2,21</t>
+          <t>-5,08; 2,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 4,47</t>
+          <t>-7,97; 4,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 247,09</t>
+          <t>-100,0; 230,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 6,45</t>
+          <t>-2,37; 6,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 1,87</t>
+          <t>-4,32; 1,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,95; -1,04</t>
+          <t>-6,1; -0,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 3,1</t>
+          <t>-8,28; 2,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,9; 758,18</t>
+          <t>-71,73; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 403,1</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 2,97</t>
+          <t>-8,03; 2,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,62</t>
+          <t>-2,56; 1,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 2,4</t>
+          <t>-7,08; 2,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 7,16</t>
+          <t>-1,64; 6,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-90,56; 137,43</t>
+          <t>-92,1; 85,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 387,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,32</t>
+          <t>-2,53; 1,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 3,05</t>
+          <t>-2,65; 3,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,88</t>
+          <t>-2,6; 1,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 1,09</t>
+          <t>-4,68; 1,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-71,31; 208,84</t>
+          <t>-74,84; 176,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,41; 151,65</t>
+          <t>-59,06; 158,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-80,14; 259,66</t>
+          <t>-80,11; 242,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,25; 54,54</t>
+          <t>-80,25; 62,47</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 6,25</t>
+          <t>-1,24; 6,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 2,95</t>
+          <t>-3,82; 2,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 4,73</t>
+          <t>-3,06; 4,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 1,54</t>
+          <t>-4,2; 1,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-55,96; 534,38</t>
+          <t>-44,9; 729,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-86,58; 226,43</t>
+          <t>-85,97; 250,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-68,37; 345,58</t>
+          <t>-75,87; 332,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 255,36</t>
+          <t>-100,0; 415,72</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 5,16</t>
+          <t>-1,85; 5,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 0,0</t>
+          <t>-6,41; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 7,92</t>
+          <t>-1,12; 7,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,73; -0,96</t>
+          <t>-13,2; -1,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,85</t>
+          <t>-0,93; 2,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,67</t>
+          <t>-1,8; 0,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,8</t>
+          <t>-2,06; 0,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,08</t>
+          <t>-3,25; 0,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-31,77; 91,37</t>
+          <t>-30,0; 104,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-62,17; 43,01</t>
+          <t>-59,56; 38,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-55,89; 38,25</t>
+          <t>-58,11; 38,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-69,15; 7,67</t>
+          <t>-68,85; 9,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1001-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>154,89%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 4,98</t>
+          <t>-0,51; 5,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 0,0</t>
+          <t>-6,76; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 2,22</t>
+          <t>-5,1; 2,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 4,33</t>
+          <t>-1,05; 6,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 230,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,94</t>
+          <t>-2,11</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-42,86%</t>
+          <t>-43,75%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 6,54</t>
+          <t>-2,22; 6,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 1,81</t>
+          <t>-3,99; 1,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,1; -0,98</t>
+          <t>-6,06; -0,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 2,87</t>
+          <t>-8,49; 2,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,73; —</t>
+          <t>-69,62; inf</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,61</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 2,0</t>
+          <t>-8,4; 2,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -870,17 +870,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 2,42</t>
+          <t>-7,25; 2,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 6,1</t>
+          <t>-1,87; 5,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-92,1; 85,46</t>
+          <t>-100,0; 91,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 387,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-1,34</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-41,77%</t>
+          <t>-31,19%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,93</t>
+          <t>-2,5; 2,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 3,12</t>
+          <t>-2,62; 3,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,99</t>
+          <t>-2,27; 1,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,28</t>
+          <t>-4,45; 1,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-74,84; 176,39</t>
+          <t>-72,39; 189,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,06; 158,15</t>
+          <t>-59,01; 169,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-80,11; 242,64</t>
+          <t>-74,95; 225,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,25; 62,47</t>
+          <t>-79,11; 86,44</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,44</t>
+          <t>-1,64</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-52,69%</t>
+          <t>-56,08%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 6,85</t>
+          <t>-1,4; 6,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 2,54</t>
+          <t>-3,7; 2,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 4,68</t>
+          <t>-3,09; 4,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,56</t>
+          <t>-4,59; 1,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-44,9; 729,99</t>
+          <t>-48,8; 690,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-85,97; 250,37</t>
+          <t>-82,38; 268,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-75,87; 332,69</t>
+          <t>-74,59; 320,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 415,72</t>
+          <t>-100,0; 217,99</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-5,6</t>
+          <t>-5,01</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-90,8%</t>
+          <t>-91,2%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 5,42</t>
+          <t>-1,83; 5,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 0,0</t>
+          <t>-6,62; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 7,85</t>
+          <t>-1,07; 7,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,2; -1,29</t>
+          <t>-10,83; -0,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-1,07</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-40,85%</t>
+          <t>-31,27%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,01</t>
+          <t>-1,09; 1,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,73</t>
+          <t>-1,72; 0,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,71</t>
+          <t>-1,88; 0,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,2</t>
+          <t>-2,68; 0,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 104,47</t>
+          <t>-35,25; 88,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-59,56; 38,35</t>
+          <t>-56,24; 47,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-58,11; 38,55</t>
+          <t>-55,37; 38,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-68,85; 9,2</t>
+          <t>-64,73; 23,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1001-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,175 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,75</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,75</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>277,35%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-38,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>154,89%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.74802620479284</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.750034648260238</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.345171341367971</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.361467632365073</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>2.773503004659241</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.3847999418751132</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1.548854265104</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-0,51; 5,05</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,76; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,1; 2,45</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-1,05; 6,87</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.506867777828775</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.756979515428493</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.096991587452497</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.054763174835327</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.048454080049359</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.450684156678375</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.87233943519123</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,72</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,11</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>69,81%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-39,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-43,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,22; 6,16</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,99; 1,99</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-6,06; -0,97</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-8,49; 2,8</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-69,62; inf</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.809024574972442</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.8347554420201815</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.71977387140829</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-2.107672229395363</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.6980681815384785</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3916402536845534</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.4374909089230275</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,21</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,36</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-51,63%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-5,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-52,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>65,81%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.219275094599965</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.994197193413373</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-6.060246066621444</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-8.487009154926531</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6961996700400254</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-8,4; 2,21</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,56; 1,63</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-7,25; 2,5</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,87; 5,61</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 91,01</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.163040502413416</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.992606530199603</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-0.9744056402643527</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.798786408561757</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +795,187 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,22</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,34</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-9,94%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-11,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-31,19%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.214039680354228</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.04652017465792638</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-2.360881474023973</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.6057569949087349</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.5163351141516925</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.05460203179645803</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.5245799035659421</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.6581360088063467</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,5; 2,32</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,62; 3,06</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 1,96</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,45; 1,97</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-72,39; 189,58</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-59,01; 169,86</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-74,95; 225,07</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-79,11; 86,44</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-8.401805094234675</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.55915344858535</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.253574918118447</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.8721390077226</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.207811390711035</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.63327581194476</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.50142496943285</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.611293260765265</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.9100866581437592</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,12</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,47</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,64</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>79,23%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-15,38%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>21,7%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-56,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,4; 6,44</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,7; 2,98</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,09; 4,37</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,59; 1,02</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-48,8; 690,69</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-82,38; 268,17</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-74,59; 320,18</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 217,99</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.2381581411638176</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1126279993647554</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.2247262878273468</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.341454072060417</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.09943448459631377</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.03420012140372517</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1117187225755734</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.3118645156314275</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-1,85</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2,89</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-5,01</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>139,25%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>270,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-91,2%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.497622721091189</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.618649876587993</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.273778332184613</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.447387212384835</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7238955084721909</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5900601288889097</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.7494654190468331</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.7910909877700942</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-1,83; 5,7</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-6,62; 0,0</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-1,07; 7,85</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-10,83; -0,91</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.318727919267254</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.064458185899939</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.957791534779338</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.973555086742291</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.895844924609205</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.698608204388804</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.250692383298261</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.8643868453916341</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +983,281 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,55</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,07</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,36%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-22,86%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-20,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-31,27%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>2.120261853180986</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.4671030810380439</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.6577904168236011</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.641794937503058</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.7922526256146569</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.153782660734928</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.2170474481698602</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.5608033298552352</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,09; 1,79</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-1,72; 0,76</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,88; 0,74</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-2,68; 0,6</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-35,25; 88,78</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-56,24; 47,76</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-55,37; 38,37</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-64,73; 23,82</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.396133712209135</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.698969710772567</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.094618924429126</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.590198112091848</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4880016331052455</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.8238228794306768</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.7459120635206415</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.436363693817465</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.977191671713829</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.371367690590025</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.01800588114261</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>6.906926743585621</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2.681694080323261</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>3.201760423798596</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>2.179948301630309</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1.258262914321362</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-1.849326178314116</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2.893819617450617</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-5.010435473723754</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>1.392542199351774</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>2.706235054208848</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.9119689759359981</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-1.831444889143836</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-6.622775208686051</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-1.067103219022111</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-10.82942486585569</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>5.695385419341678</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>7.854257692012241</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-0.91353190032811</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.4023122200731262</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.5591006371666485</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.5459909242718948</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-1.069268198319383</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.1536414926159642</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.2285933027942195</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.2012738855071287</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.3126884867380214</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.09015129304116</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.72217964005523</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.883211207256352</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-2.68038133760499</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.3524567049861253</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.562425254891511</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.5537465097945914</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.6473469187206182</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.79456508789529</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.7638486194597683</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.7373333883907554</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.5981052354441355</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.8877916655051165</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.4776026961748934</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.3836614256035152</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.2381907329499872</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1265,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
